--- a/2_SQL_database/Data_clean_updated/MCAS/Estados_US/Edos_USA_2013/NEW_JERSEY_2013.xlsx
+++ b/2_SQL_database/Data_clean_updated/MCAS/Estados_US/Edos_USA_2013/NEW_JERSEY_2013.xlsx
@@ -4020,7 +4020,7 @@
       </c>
       <c r="B204" t="inlineStr">
         <is>
-          <t>Allende</t>
+          <t>San Miguel De Allende</t>
         </is>
       </c>
       <c r="C204">
@@ -12282,7 +12282,7 @@
       </c>
       <c r="B663" t="inlineStr">
         <is>
-          <t>San Juan Mixtepec - Distr. 08 -</t>
+          <t>San Juan Mixtepec -Dto. 08 -</t>
         </is>
       </c>
       <c r="C663">
@@ -13398,7 +13398,7 @@
       </c>
       <c r="B725" t="inlineStr">
         <is>
-          <t>San Pedro Mixtepec - Distr. 22 -</t>
+          <t>San Pedro Mixtepec -Dto. 22 -</t>
         </is>
       </c>
       <c r="C725">
@@ -13560,7 +13560,7 @@
       </c>
       <c r="B734" t="inlineStr">
         <is>
-          <t>San Pedro Totolapa</t>
+          <t>San Pedro Totolapam</t>
         </is>
       </c>
       <c r="C734">
@@ -21246,7 +21246,7 @@
       </c>
       <c r="B1161" t="inlineStr">
         <is>
-          <t>Yauhquemecan</t>
+          <t>Yauhquemehcan</t>
         </is>
       </c>
       <c r="C1161">
@@ -23478,7 +23478,7 @@
       </c>
       <c r="B1285" t="inlineStr">
         <is>
-          <t>Tuxpam</t>
+          <t>Tuxpan</t>
         </is>
       </c>
       <c r="C1285">
